--- a/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0179</v>
+        <v>-0.0219</v>
       </c>
       <c r="G2">
-        <v>0.3395733565520244</v>
+        <v>0.1817073170731708</v>
       </c>
       <c r="H2">
-        <v>0.3395733565520244</v>
+        <v>0.1817073170731708</v>
       </c>
       <c r="I2">
-        <v>-0.09949323347792752</v>
+        <v>-0.1529156544331356</v>
       </c>
       <c r="J2">
-        <v>-0.09949323347792752</v>
+        <v>-0.1529156544331356</v>
       </c>
       <c r="K2">
-        <v>-107.4</v>
+        <v>-150.3</v>
       </c>
       <c r="L2">
-        <v>-0.2337831954723553</v>
+        <v>-0.3054878048780488</v>
       </c>
       <c r="M2">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.735229759299781e-06</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-1.86219739292365e-05</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.002</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>67.5</v>
+        <v>31.9</v>
       </c>
       <c r="V2">
-        <v>0.09231400437636761</v>
+        <v>0.1835443037974683</v>
       </c>
       <c r="W2">
-        <v>-0.1705574082896617</v>
+        <v>-0.372398414271556</v>
       </c>
       <c r="X2">
-        <v>0.1206473882520507</v>
+        <v>0.223549214382523</v>
       </c>
       <c r="Y2">
-        <v>-0.2912047965417124</v>
+        <v>-0.595947628654079</v>
       </c>
       <c r="Z2">
-        <v>0.5049261862148279</v>
+        <v>0.6187725713594319</v>
       </c>
       <c r="AA2">
-        <v>-0.05023673893419138</v>
+        <v>-0.09462001269470161</v>
       </c>
       <c r="AB2">
-        <v>0.09365383575199421</v>
+        <v>0.1732471480984807</v>
       </c>
       <c r="AC2">
-        <v>-0.1438905746861856</v>
+        <v>-0.2678671607931823</v>
       </c>
       <c r="AD2">
-        <v>1322.8</v>
+        <v>1435.2</v>
       </c>
       <c r="AE2">
-        <v>1.535957298799509</v>
+        <v>1.022509905513523</v>
       </c>
       <c r="AF2">
-        <v>1324.335957298799</v>
+        <v>1436.222509905514</v>
       </c>
       <c r="AG2">
-        <v>1256.835957298799</v>
+        <v>1404.322509905513</v>
       </c>
       <c r="AH2">
-        <v>0.6442776895224556</v>
+        <v>0.8920511987064084</v>
       </c>
       <c r="AI2">
-        <v>0.7630703078949775</v>
+        <v>0.7935270720404992</v>
       </c>
       <c r="AJ2">
-        <v>0.6321998114191546</v>
+        <v>0.8898691331572187</v>
       </c>
       <c r="AK2">
-        <v>0.753482532435396</v>
+        <v>0.789822683392316</v>
       </c>
       <c r="AL2">
-        <v>58.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AM2">
-        <v>58.053</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="AN2">
-        <v>10.95940347970174</v>
+        <v>20.22262927997746</v>
       </c>
       <c r="AO2">
-        <v>-0.8061749571183534</v>
+        <v>-1.045267489711934</v>
       </c>
       <c r="AP2">
-        <v>10.41289111266611</v>
+        <v>19.7875512174935</v>
       </c>
       <c r="AQ2">
-        <v>-0.8096050161059721</v>
+        <v>-1.061281337047354</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0179</v>
+        <v>-0.0219</v>
       </c>
       <c r="G3">
-        <v>0.3395733565520244</v>
+        <v>0.1817073170731708</v>
       </c>
       <c r="H3">
-        <v>0.3395733565520244</v>
+        <v>0.1817073170731708</v>
       </c>
       <c r="I3">
-        <v>-0.09949323347792752</v>
+        <v>-0.1529156544331356</v>
       </c>
       <c r="J3">
-        <v>-0.09949323347792752</v>
+        <v>-0.1529156544331356</v>
       </c>
       <c r="K3">
-        <v>-107.4</v>
+        <v>-150.3</v>
       </c>
       <c r="L3">
-        <v>-0.2337831954723553</v>
+        <v>-0.3054878048780488</v>
       </c>
       <c r="M3">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>2.735229759299781e-06</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-1.86219739292365e-05</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.002</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>67.5</v>
+        <v>31.9</v>
       </c>
       <c r="V3">
-        <v>0.09231400437636761</v>
+        <v>0.1835443037974683</v>
       </c>
       <c r="W3">
-        <v>-0.1705574082896617</v>
+        <v>-0.372398414271556</v>
       </c>
       <c r="X3">
-        <v>0.1206473882520507</v>
+        <v>0.223549214382523</v>
       </c>
       <c r="Y3">
-        <v>-0.2912047965417124</v>
+        <v>-0.595947628654079</v>
       </c>
       <c r="Z3">
-        <v>0.5049261862148279</v>
+        <v>0.6187725713594319</v>
       </c>
       <c r="AA3">
-        <v>-0.05023673893419138</v>
+        <v>-0.09462001269470161</v>
       </c>
       <c r="AB3">
-        <v>0.09365383575199421</v>
+        <v>0.1732471480984807</v>
       </c>
       <c r="AC3">
-        <v>-0.1438905746861856</v>
+        <v>-0.2678671607931823</v>
       </c>
       <c r="AD3">
-        <v>1322.8</v>
+        <v>1435.2</v>
       </c>
       <c r="AE3">
-        <v>1.535957298799509</v>
+        <v>1.022509905513523</v>
       </c>
       <c r="AF3">
-        <v>1324.335957298799</v>
+        <v>1436.222509905514</v>
       </c>
       <c r="AG3">
-        <v>1256.835957298799</v>
+        <v>1404.322509905513</v>
       </c>
       <c r="AH3">
-        <v>0.6442776895224556</v>
+        <v>0.8920511987064084</v>
       </c>
       <c r="AI3">
-        <v>0.7630703078949775</v>
+        <v>0.7935270720404992</v>
       </c>
       <c r="AJ3">
-        <v>0.6321998114191546</v>
+        <v>0.8898691331572187</v>
       </c>
       <c r="AK3">
-        <v>0.753482532435396</v>
+        <v>0.789822683392316</v>
       </c>
       <c r="AL3">
-        <v>58.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AM3">
-        <v>58.053</v>
+        <v>71.80000000000001</v>
       </c>
       <c r="AN3">
-        <v>10.95940347970174</v>
+        <v>20.22262927997746</v>
       </c>
       <c r="AO3">
-        <v>-0.8061749571183534</v>
+        <v>-1.045267489711934</v>
       </c>
       <c r="AP3">
-        <v>10.41289111266611</v>
+        <v>19.7875512174935</v>
       </c>
       <c r="AQ3">
-        <v>-0.8096050161059721</v>
+        <v>-1.061281337047354</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0219</v>
+        <v>-0.0199</v>
       </c>
       <c r="G2">
-        <v>0.1817073170731708</v>
+        <v>0.1228203184230477</v>
       </c>
       <c r="H2">
-        <v>0.1817073170731708</v>
+        <v>0.1228203184230477</v>
       </c>
       <c r="I2">
-        <v>-0.1529156544331356</v>
+        <v>-0.1854428162786859</v>
       </c>
       <c r="J2">
-        <v>-0.1529156544331356</v>
+        <v>-0.1854428162786859</v>
       </c>
       <c r="K2">
-        <v>-150.3</v>
+        <v>-230.3</v>
       </c>
       <c r="L2">
-        <v>-0.3054878048780488</v>
+        <v>-0.4365049279757392</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>31.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1835443037974683</v>
+        <v>0.7068403908794788</v>
       </c>
       <c r="W2">
-        <v>-0.372398414271556</v>
+        <v>-0.6302681992337166</v>
       </c>
       <c r="X2">
-        <v>0.223549214382523</v>
+        <v>0.4544055945647961</v>
       </c>
       <c r="Y2">
-        <v>-0.595947628654079</v>
+        <v>-1.084673793798513</v>
       </c>
       <c r="Z2">
-        <v>0.6187725713594319</v>
+        <v>0.6304608553106124</v>
       </c>
       <c r="AA2">
-        <v>-0.09462001269470161</v>
+        <v>-0.1169144365622691</v>
       </c>
       <c r="AB2">
-        <v>0.1732471480984807</v>
+        <v>0.09002347128689335</v>
       </c>
       <c r="AC2">
-        <v>-0.2678671607931823</v>
+        <v>-0.2069379078491624</v>
       </c>
       <c r="AD2">
-        <v>1435.2</v>
+        <v>1962.8</v>
       </c>
       <c r="AE2">
-        <v>1.022509905513523</v>
+        <v>1.648149343173409</v>
       </c>
       <c r="AF2">
-        <v>1436.222509905514</v>
+        <v>1964.448149343173</v>
       </c>
       <c r="AG2">
-        <v>1404.322509905513</v>
+        <v>1899.348149343173</v>
       </c>
       <c r="AH2">
-        <v>0.8920511987064084</v>
+        <v>0.9552162199414512</v>
       </c>
       <c r="AI2">
-        <v>0.7935270720404992</v>
+        <v>0.9223418814853032</v>
       </c>
       <c r="AJ2">
-        <v>0.8898691331572187</v>
+        <v>0.9537522480661238</v>
       </c>
       <c r="AK2">
-        <v>0.789822683392316</v>
+        <v>0.9198933777697701</v>
       </c>
       <c r="AL2">
-        <v>72.90000000000001</v>
+        <v>139.7</v>
       </c>
       <c r="AM2">
-        <v>71.80000000000001</v>
+        <v>138.62</v>
       </c>
       <c r="AN2">
-        <v>20.22262927997746</v>
+        <v>39.8214648001623</v>
       </c>
       <c r="AO2">
-        <v>-1.045267489711934</v>
+        <v>-0.7100930565497495</v>
       </c>
       <c r="AP2">
-        <v>19.7875512174935</v>
+        <v>38.53414788685684</v>
       </c>
       <c r="AQ2">
-        <v>-1.061281337047354</v>
+        <v>-0.7156254508728901</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0219</v>
+        <v>-0.0199</v>
       </c>
       <c r="G3">
-        <v>0.1817073170731708</v>
+        <v>0.1228203184230477</v>
       </c>
       <c r="H3">
-        <v>0.1817073170731708</v>
+        <v>0.1228203184230477</v>
       </c>
       <c r="I3">
-        <v>-0.1529156544331356</v>
+        <v>-0.1854428162786859</v>
       </c>
       <c r="J3">
-        <v>-0.1529156544331356</v>
+        <v>-0.1854428162786859</v>
       </c>
       <c r="K3">
-        <v>-150.3</v>
+        <v>-230.3</v>
       </c>
       <c r="L3">
-        <v>-0.3054878048780488</v>
+        <v>-0.4365049279757392</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.9</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1835443037974683</v>
+        <v>0.7068403908794788</v>
       </c>
       <c r="W3">
-        <v>-0.372398414271556</v>
+        <v>-0.6302681992337166</v>
       </c>
       <c r="X3">
-        <v>0.223549214382523</v>
+        <v>0.4544055945647961</v>
       </c>
       <c r="Y3">
-        <v>-0.595947628654079</v>
+        <v>-1.084673793798513</v>
       </c>
       <c r="Z3">
-        <v>0.6187725713594319</v>
+        <v>0.6304608553106124</v>
       </c>
       <c r="AA3">
-        <v>-0.09462001269470161</v>
+        <v>-0.1169144365622691</v>
       </c>
       <c r="AB3">
-        <v>0.1732471480984807</v>
+        <v>0.09002347128689335</v>
       </c>
       <c r="AC3">
-        <v>-0.2678671607931823</v>
+        <v>-0.2069379078491624</v>
       </c>
       <c r="AD3">
-        <v>1435.2</v>
+        <v>1962.8</v>
       </c>
       <c r="AE3">
-        <v>1.022509905513523</v>
+        <v>1.648149343173409</v>
       </c>
       <c r="AF3">
-        <v>1436.222509905514</v>
+        <v>1964.448149343173</v>
       </c>
       <c r="AG3">
-        <v>1404.322509905513</v>
+        <v>1899.348149343173</v>
       </c>
       <c r="AH3">
-        <v>0.8920511987064084</v>
+        <v>0.9552162199414512</v>
       </c>
       <c r="AI3">
-        <v>0.7935270720404992</v>
+        <v>0.9223418814853032</v>
       </c>
       <c r="AJ3">
-        <v>0.8898691331572187</v>
+        <v>0.9537522480661238</v>
       </c>
       <c r="AK3">
-        <v>0.789822683392316</v>
+        <v>0.9198933777697701</v>
       </c>
       <c r="AL3">
-        <v>72.90000000000001</v>
+        <v>139.7</v>
       </c>
       <c r="AM3">
-        <v>71.80000000000001</v>
+        <v>138.62</v>
       </c>
       <c r="AN3">
-        <v>20.22262927997746</v>
+        <v>39.8214648001623</v>
       </c>
       <c r="AO3">
-        <v>-1.045267489711934</v>
+        <v>-0.7100930565497495</v>
       </c>
       <c r="AP3">
-        <v>19.7875512174935</v>
+        <v>38.53414788685684</v>
       </c>
       <c r="AQ3">
-        <v>-1.061281337047354</v>
+        <v>-0.7156254508728901</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_cable_tv.xlsx
@@ -639,10 +639,10 @@
         <v>-0.6302681992337166</v>
       </c>
       <c r="X2">
-        <v>0.4544055945647961</v>
+        <v>0.4541428974968313</v>
       </c>
       <c r="Y2">
-        <v>-1.084673793798513</v>
+        <v>-1.084411096730548</v>
       </c>
       <c r="Z2">
         <v>0.6304608553106124</v>
@@ -651,10 +651,10 @@
         <v>-0.1169144365622691</v>
       </c>
       <c r="AB2">
-        <v>0.09002347128689335</v>
+        <v>0.0900117067191796</v>
       </c>
       <c r="AC2">
-        <v>-0.2069379078491624</v>
+        <v>-0.2069261432814486</v>
       </c>
       <c r="AD2">
         <v>1962.8</v>
@@ -767,10 +767,10 @@
         <v>-0.6302681992337166</v>
       </c>
       <c r="X3">
-        <v>0.4544055945647961</v>
+        <v>0.4541428974968313</v>
       </c>
       <c r="Y3">
-        <v>-1.084673793798513</v>
+        <v>-1.084411096730548</v>
       </c>
       <c r="Z3">
         <v>0.6304608553106124</v>
@@ -779,10 +779,10 @@
         <v>-0.1169144365622691</v>
       </c>
       <c r="AB3">
-        <v>0.09002347128689335</v>
+        <v>0.0900117067191796</v>
       </c>
       <c r="AC3">
-        <v>-0.2069379078491624</v>
+        <v>-0.2069261432814486</v>
       </c>
       <c r="AD3">
         <v>1962.8</v>
